--- a/data/manual/ukrajna_oroszorszag_melysegi_csapasok.xlsx
+++ b/data/manual/ukrajna_oroszorszag_melysegi_csapasok.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orsolya\OneDrive - Budapesti Vasutas Sport Club - Zugló Közhasznú Egyesület\Asztal\Osint\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.hetzer\Desktop\Desktop\Hetzer Miklos\Orsi\Repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F63BAE12-9E7A-43B9-ACAA-6B35F528A50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9B40403-E439-41C2-8644-F1699EEBE0A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Összesítés" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="692">
   <si>
     <t>MÉLYSÉGI CSAPÁSOK – 2026.07.13–07.27.</t>
   </si>
@@ -1738,6 +1738,366 @@
   </si>
   <si>
     <t>Városközponti összesítő koordináta; több becsapódási pont</t>
+  </si>
+  <si>
+    <t>Adler / Szocsi repülőtér</t>
+  </si>
+  <si>
+    <t>Katonai repülési eszközök / légvédelem</t>
+  </si>
+  <si>
+    <t>Ukrán csapások érték az Adler–Szocsi térségét. Nyílt forrású BDA szerint Mi-28 és Ka-52 harci helikopterek semmisültek meg, egy Mi-8 pedig megsérült.</t>
+  </si>
+  <si>
+    <t>Repülőtéri közelítő koordináta; BDA később vált elérhetővé</t>
+  </si>
+  <si>
+    <t>https://understandingwar.org/research/russia-ukraine/russian-offensive-campaign-assessment-september-6-2026/</t>
+  </si>
+  <si>
+    <t>Adler / Szocsi – Rosneft olajdepó</t>
+  </si>
+  <si>
+    <t>Olajdepó / energia-infrastruktúra</t>
+  </si>
+  <si>
+    <t>Ukrán csapás érte a Rosneft szocsi olajdepóját. Műholdképes értékelés szerint kilenc tartály megsemmisült, és légvédelmi eszközök is célponttá váltak.</t>
+  </si>
+  <si>
+    <t>Szocsi/Adler ipari térség közelítő koordináta</t>
+  </si>
+  <si>
+    <t>Sterlitamak petrolkémiai és Avangard hadiipari üzem</t>
+  </si>
+  <si>
+    <t>Petrolkémiai / hadiipari infrastruktúra</t>
+  </si>
+  <si>
+    <t>Nyílt források szerint ukrán csapás érte a Sterlitamak petrolkémiai üzemet és az Avangard hadiipari létesítményt, mintegy 1 300 km-re az ukrán határtól.</t>
+  </si>
+  <si>
+    <t>Városközponti koordináta; több különálló objektum</t>
+  </si>
+  <si>
+    <t>https://understandingwar.org/research/russia-ukraine/russian-offensive-campaign-assessment-september-4-2026/</t>
+  </si>
+  <si>
+    <t>Ukrán dróncsapás tüzet okozott a rjazanyi olajfinomítóban; a regionális kormányzó is elismerte a tüzet.</t>
+  </si>
+  <si>
+    <t>Rosztov-na-Donu repülőtér és légvédelmi objektumok</t>
+  </si>
+  <si>
+    <t>Katonai repülőtér / radar / légvédelem</t>
+  </si>
+  <si>
+    <t>Az ukrán vezérkar szerint csapás érte a rosztovi repülőteret, egy Podlyot radart és két Pantsir-S1 légvédelmi rendszert.</t>
+  </si>
+  <si>
+    <t>Repülőtéri/térségi közelítő koordináta; több célpont</t>
+  </si>
+  <si>
+    <t>Lukoil Perm olajfinomító</t>
+  </si>
+  <si>
+    <t>Ukrán erők ismét a permi olajfinomítót támadták. A regionális kormányzó megerősítette az ukrán dróncsapást.</t>
+  </si>
+  <si>
+    <t>Létesítményi/települési közelítő koordináta</t>
+  </si>
+  <si>
+    <t>https://understandingwar.org/research/russia-ukraine/russian-offensive-campaign-assessment-september-7-2026/</t>
+  </si>
+  <si>
+    <t>Geolokált felvételek alapján ukrán drónok csapást mértek a szaratovi olajfinomítóra; a regionális hatóságok dróntámadást ismertek el.</t>
+  </si>
+  <si>
+    <t>https://understandingwar.org/research/russia-ukraine/russian-offensive-campaign-assessment-september-8-2026/</t>
+  </si>
+  <si>
+    <t>Jamali-Nyenyec Autonóm Körzet</t>
+  </si>
+  <si>
+    <t>Novy Urengoy gázkondenzátum-kezelő üzem</t>
+  </si>
+  <si>
+    <t>Gázfeldolgozó infrastruktúra</t>
+  </si>
+  <si>
+    <t>Ukrán különleges erők csapást mértek a Novy Urengoy gázkomplexumra. Ez a kampány egyik legmélyebb, közel 3 000 km-es csapása volt.</t>
+  </si>
+  <si>
+    <t>Városi/ipari térség közelítő koordináta</t>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/europe/russian-drones-kill-injure-people-ukraine-moldova-border-crossing-2026-09-09/</t>
+  </si>
+  <si>
+    <t>Purovsky gázfeldolgozó üzem</t>
+  </si>
+  <si>
+    <t>Ukrán különleges erők a Purovsky gázfeldolgozó üzemet is támadták; a két nyugat-szibériai célpont a háború addigi legnagyobb csapásmélységét jelezte.</t>
+  </si>
+  <si>
+    <t>Létesítményi térség közelítő koordináta</t>
+  </si>
+  <si>
+    <t>https://understandingwar.org/research/russia-ukraine/russian-offensive-campaign-assessment-september-10-2026/</t>
+  </si>
+  <si>
+    <t>Novorosszijszki haditengerészeti bázis</t>
+  </si>
+  <si>
+    <t>UAV / tengeri drón</t>
+  </si>
+  <si>
+    <t>Haditengerészeti bázis / hadihajók</t>
+  </si>
+  <si>
+    <t>Ukrán csapás érte a novorosszijszki haditengerészeti infrastruktúrát. Későbbi ukrán BDA szerint több hadihajó, köztük az Admiral Essen fregatt is megsérült.</t>
+  </si>
+  <si>
+    <t>Kikötői térség közelítő koordináta</t>
+  </si>
+  <si>
+    <t>Mahacskala tengeri kereskedelmi kikötő</t>
+  </si>
+  <si>
+    <t>Kikötő / logisztikai infrastruktúra</t>
+  </si>
+  <si>
+    <t>Ukrán dróncsapás érte a Kaszpi-tenger fontos mélyvízi kikötőjét Mahacskalában; a támadás után tűz keletkezett.</t>
+  </si>
+  <si>
+    <t>Kikötői/városi közelítő koordináta</t>
+  </si>
+  <si>
+    <t>Szaratovi olajfinomító és Ozon logisztikai központ</t>
+  </si>
+  <si>
+    <t>Olajfinomító / logisztikai infrastruktúra</t>
+  </si>
+  <si>
+    <t>Az ukrán csapáshullám ismét elérte a szaratovi finomítót; emellett az Ozon logisztikai központjában is tűz keletkezett.</t>
+  </si>
+  <si>
+    <t>Városi összesítő koordináta; két különálló objektum</t>
+  </si>
+  <si>
+    <t>https://understandingwar.org/research/russia-ukraine/russian-offensive-campaign-assessment-september-11-2026/</t>
+  </si>
+  <si>
+    <t>Tolyattikauchuk petrolkémiai üzem, Togliatti</t>
+  </si>
+  <si>
+    <t>Petrolkémiai / hadiipari beszállítói infrastruktúra</t>
+  </si>
+  <si>
+    <t>Az ukrán vezérkar szerint csapás érte a Tolyattikauchuk üzemet, amely ballisztikus rakéták szilárd hajtóanyagához használt alapanyagokat is gyárt.</t>
+  </si>
+  <si>
+    <t>Városi/létesítményi közelítő koordináta</t>
+  </si>
+  <si>
+    <t>https://understandingwar.org/research/russia-ukraine/russian-offensive-campaign-assessment-september-12-2026/</t>
+  </si>
+  <si>
+    <t>Slavyansk olajfinomító, Szlavjanszk-na-Kubani</t>
+  </si>
+  <si>
+    <t>Ukrán csapás érte a Slavyansk finomítót. Későbbi BDA szerint három tárolótartály megsemmisült és további nyolc megsérült.</t>
+  </si>
+  <si>
+    <t>Létesítményi közelítő koordináta</t>
+  </si>
+  <si>
+    <t>https://understandingwar.org/research/russia-ukraine/russian-offensive-campaign-assessment-september-15-2026/</t>
+  </si>
+  <si>
+    <t>Újabb ukrán dróncsapás érte a TANECO finomítót; orosz regionális források tüzet ismertek el.</t>
+  </si>
+  <si>
+    <t>https://understandingwar.org/research/russia-ukraine/russian-offensive-campaign-assessment-september-13-2026/</t>
+  </si>
+  <si>
+    <t>Szocsi – S-400 92N6 radar</t>
+  </si>
+  <si>
+    <t>Légvédelmi radar</t>
+  </si>
+  <si>
+    <t>Az ukrán vezérkar szerint csapás érte az S-400 rendszer 92N6 multifunkciós radarját Szocsi térségében.</t>
+  </si>
+  <si>
+    <t>Városi/térségi közelítő koordináta</t>
+  </si>
+  <si>
+    <t>https://understandingwar.org/research/russia-ukraine/russian-offensive-campaign-assessment-september-14-2026/</t>
+  </si>
+  <si>
+    <t>Ukrán csapás érte a szizranyi finomítót. Az ukrán vezérkar szerint az AVT-6 elsődleges feldolgozóegység és egy tartálypark is megsérült.</t>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/europe/russia-hits-petrol-station-warehouse-facilities-kyiv-mayor-says-2026-09-15/</t>
+  </si>
+  <si>
+    <t>Atlant Aero, Taganrog</t>
+  </si>
+  <si>
+    <t>Dróngyártó hadiipari létesítmény</t>
+  </si>
+  <si>
+    <t>Ukrán csapás érte az Atlant Aero létesítményt, amely Molniya drónokat és Orion felderítő drónalkatrészeket gyárt. BDA szerint több gyártó- és raktárépület sérült vagy megsemmisült.</t>
+  </si>
+  <si>
+    <t>Coca-Cola üzem, Brovary térsége</t>
+  </si>
+  <si>
+    <t>Shahed-típusú UAV</t>
+  </si>
+  <si>
+    <t>Ipari / kereskedelmi infrastruktúra</t>
+  </si>
+  <si>
+    <t>Orosz drónok megrongálták a Coca-Cola Kijev melletti üzemét. Személyi sérülést nem jelentettek.</t>
+  </si>
+  <si>
+    <t>Brovary térségi közelítő koordináta</t>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/ukraines-zelenskiy-says-russian-drones-hit-coca-cola-plant-outside-kyiv-2026-09-03/</t>
+  </si>
+  <si>
+    <t>Ballisztikus és cirkálórakéták + UAV-k</t>
+  </si>
+  <si>
+    <t>Lakó-, oktatási, egészségügyi és raktári infrastruktúra</t>
+  </si>
+  <si>
+    <t>A háromnapos fővárosi csapásszünet után nagyszabású orosz támadás érte Kijevet. Legalább 14 magasépület, kollégium, iskola, klinika és raktárak sérültek; öt halálos áldozatot jelentettek.</t>
+  </si>
+  <si>
+    <t>Városközponti összesítő koordináta; több becsapódási hely</t>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/europe/russian-ballistic-missiles-hit-kyiv-us-envoys-leave-2026-09-08/</t>
+  </si>
+  <si>
+    <t>Szumii terület</t>
+  </si>
+  <si>
+    <t>Személyvonatok, Szumii terület</t>
+  </si>
+  <si>
+    <t>Vasúti / személyszállítási infrastruktúra</t>
+  </si>
+  <si>
+    <t>Orosz drónok személyvonatokat támadtak a Szumii területen; közel száz embert evakuáltak, és repeszsérülésekről számoltak be.</t>
+  </si>
+  <si>
+    <t>Szumi városközponti összesítő koordináta; több vasúti esemény</t>
+  </si>
+  <si>
+    <t>Zaporizzsja – személyvonat</t>
+  </si>
+  <si>
+    <t>Kettős UAV-csapás</t>
+  </si>
+  <si>
+    <t>Orosz kettős dróncsapás ért egy személyvonatot Zaporizzsjában; egy vasúti dolgozó meghalt, az utasokat evakuálták.</t>
+  </si>
+  <si>
+    <t>Városközponti koordináta; pontos vasúti pont nem közölt</t>
+  </si>
+  <si>
+    <t>Starokozache / Tudora határátkelő</t>
+  </si>
+  <si>
+    <t>Határ- és kereskedelmi logisztikai infrastruktúra</t>
+  </si>
+  <si>
+    <t>Orosz dróncsapás érte az ukrán–moldovai határátkelőt. Két ember meghalt, három megsérült, a forgalmat leállították.</t>
+  </si>
+  <si>
+    <t>Sumy – bevásárlóközpont</t>
+  </si>
+  <si>
+    <t>Kereskedelmi infrastruktúra</t>
+  </si>
+  <si>
+    <t>Orosz dróncsapás ért egy bevásárlóközpontot Sumyban. Két halálos áldozatot és húsz sérültet jelentettek.</t>
+  </si>
+  <si>
+    <t>Városközponti koordináta; pontos objektumpont nem közölt</t>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/strike-shopping-centre-sumy-northern-ukraine-kills-three-governor-says-2026-09-09/</t>
+  </si>
+  <si>
+    <t>Kijev és több régió</t>
+  </si>
+  <si>
+    <t>Shahed/Gerbera UAV-k és Banderol</t>
+  </si>
+  <si>
+    <t>Kereskedelmi, civil, lakó- és egészségügyi infrastruktúra</t>
+  </si>
+  <si>
+    <t>Oroszország 161 drónt és egy Banderol lőszert indított. Találatokat 19 helyszínen rögzítettek; Kijevben mentőalakulatok ellen kettős csapást is jelentettek.</t>
+  </si>
+  <si>
+    <t>Összesítő koordináta; nem egyetlen becsapódási hely</t>
+  </si>
+  <si>
+    <t>Odesza régió – több célpont</t>
+  </si>
+  <si>
+    <t>Hátországi infrastruktúra</t>
+  </si>
+  <si>
+    <t>Az éjszakai támadás fő célterülete az Odesszai terület volt. Rakéták és drónok húsz helyszínt értek el az ukrán légierő közlése szerint.</t>
+  </si>
+  <si>
+    <t>Volinyi terület</t>
+  </si>
+  <si>
+    <t>Yahodyn – Kijev–Varsó személyvonat és benzinkút</t>
+  </si>
+  <si>
+    <t>Vasúti / határ- és üzemanyag-infrastruktúra</t>
+  </si>
+  <si>
+    <t>Orosz drón csapást mért a Kijev–Varsó vonat mozdonyára a lengyel határ közelében, valamint egy benzinkútra. A támadás a Yahodyn határátkelő térségét érintette.</t>
+  </si>
+  <si>
+    <t>Határátkelő térségi közelítő koordináta</t>
+  </si>
+  <si>
+    <t>Kijev – üzemanyagtöltő állomások</t>
+  </si>
+  <si>
+    <t>Üzemanyag-ellátási infrastruktúra</t>
+  </si>
+  <si>
+    <t>Orosz drónok két kijevi benzinkutat rongáltak meg. A városi hatóságok szerint 2026-ban addigra 16 töltőállomást ért orosz támadás Kijevben.</t>
+  </si>
+  <si>
+    <t>Városközponti összesítő koordináta; több töltőállomás</t>
+  </si>
+  <si>
+    <t>Energia- és kikötői infrastruktúra</t>
+  </si>
+  <si>
+    <t>Kb. 200 UAV</t>
+  </si>
+  <si>
+    <t>Energia / kikötő / kritikus infrastruktúra</t>
+  </si>
+  <si>
+    <t>Az éjszakai orosz támadási hullámban mintegy 200 drónt indítottak. Kijev mellett más régiók energia- és kikötői infrastruktúráját is találatok érték; két halálos áldozatot jelentettek országosan.</t>
+  </si>
+  <si>
+    <t>Odesza koordinátájával jelölt összesítő esemény; több régiót érint</t>
   </si>
 </sst>
 </file>
@@ -2071,7 +2431,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UkraineRussiaTable" displayName="UkraineRussiaTable" ref="A1:L64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UkraineRussiaTable" displayName="UkraineRussiaTable" ref="A1:L82">
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Dátum"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Támadó"/>
@@ -2091,7 +2451,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="RussiaUkraineTable" displayName="RussiaUkraineTable" ref="A1:L57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="RussiaUkraineTable" displayName="RussiaUkraineTable" ref="A1:L68">
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Dátum"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Támadó"/>
@@ -2444,7 +2804,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4891,6 +5251,690 @@
         <v>498</v>
       </c>
     </row>
+    <row r="65" spans="1:12" ht="42">
+      <c r="A65" s="6">
+        <v>46268</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="F65" s="8">
+        <v>43.4499</v>
+      </c>
+      <c r="G65" s="8">
+        <v>39.956600000000002</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="L65" s="7" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="56">
+      <c r="A66" s="6">
+        <v>46269</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="F66" s="8">
+        <v>43.43</v>
+      </c>
+      <c r="G66" s="8">
+        <v>39.92</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I66" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="K66" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="L66" s="7" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="42">
+      <c r="A67" s="6">
+        <v>46269</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="F67" s="8">
+        <v>53.630400000000002</v>
+      </c>
+      <c r="G67" s="8">
+        <v>55.930799999999998</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="K67" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="L67" s="7" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="42">
+      <c r="A68" s="6">
+        <v>46271</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="F68" s="8">
+        <v>54.62</v>
+      </c>
+      <c r="G68" s="8">
+        <v>39.72</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I68" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J68" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="K68" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L68" s="7" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="42">
+      <c r="A69" s="6">
+        <v>46271</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="F69" s="8">
+        <v>47.258200000000002</v>
+      </c>
+      <c r="G69" s="8">
+        <v>39.818100000000001</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="L69" s="7" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="28">
+      <c r="A70" s="6">
+        <v>46272</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="F70" s="8">
+        <v>57.99</v>
+      </c>
+      <c r="G70" s="8">
+        <v>56.18</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I70" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J70" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="K70" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="L70" s="7" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="42">
+      <c r="A71" s="6">
+        <v>46273</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="F71" s="8">
+        <v>51.442</v>
+      </c>
+      <c r="G71" s="8">
+        <v>45.96</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>595</v>
+      </c>
+      <c r="K71" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L71" s="7" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="42">
+      <c r="A72" s="6">
+        <v>46274</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="F72" s="8">
+        <v>66.083299999999994</v>
+      </c>
+      <c r="G72" s="8">
+        <v>76.633300000000006</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I72" s="7" t="s">
+        <v>599</v>
+      </c>
+      <c r="J72" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="K72" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="L72" s="7" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="42">
+      <c r="A73" s="6">
+        <v>46274</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="F73" s="8">
+        <v>64.959999999999994</v>
+      </c>
+      <c r="G73" s="8">
+        <v>77.819999999999993</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I73" s="7" t="s">
+        <v>599</v>
+      </c>
+      <c r="J73" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="K73" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="L73" s="7" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="42">
+      <c r="A74" s="6">
+        <v>46274</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="F74" s="8">
+        <v>44.724400000000003</v>
+      </c>
+      <c r="G74" s="8">
+        <v>37.767499999999998</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="I74" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="J74" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="K74" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="L74" s="7" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="28">
+      <c r="A75" s="6">
+        <v>46275</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="F75" s="8">
+        <v>42.984900000000003</v>
+      </c>
+      <c r="G75" s="8">
+        <v>47.5047</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I75" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>614</v>
+      </c>
+      <c r="K75" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="L75" s="7" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="42">
+      <c r="A76" s="6">
+        <v>46276</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="F76" s="8">
+        <v>51.5</v>
+      </c>
+      <c r="G76" s="8">
+        <v>45.95</v>
+      </c>
+      <c r="H76" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I76" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="J76" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="K76" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="L76" s="7" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="42">
+      <c r="A77" s="6">
+        <v>46277</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="F77" s="8">
+        <v>53.507800000000003</v>
+      </c>
+      <c r="G77" s="8">
+        <v>49.420400000000001</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I77" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="K77" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="L77" s="7" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="42">
+      <c r="A78" s="6">
+        <v>46278</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="F78" s="8">
+        <v>45.26</v>
+      </c>
+      <c r="G78" s="8">
+        <v>38.130000000000003</v>
+      </c>
+      <c r="H78" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I78" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J78" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="K78" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="L78" s="7" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="28">
+      <c r="A79" s="6">
+        <v>46278</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="F79" s="8">
+        <v>55.636000000000003</v>
+      </c>
+      <c r="G79" s="8">
+        <v>51.814</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I79" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="K79" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L79" s="7" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="28">
+      <c r="A80" s="6">
+        <v>46279</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="F80" s="8">
+        <v>43.585500000000003</v>
+      </c>
+      <c r="G80" s="8">
+        <v>39.723100000000002</v>
+      </c>
+      <c r="H80" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I80" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="J80" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="K80" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="L80" s="7" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="42">
+      <c r="A81" s="6">
+        <v>46280</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="F81" s="8">
+        <v>53.155000000000001</v>
+      </c>
+      <c r="G81" s="8">
+        <v>48.473999999999997</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I81" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="K81" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L81" s="7" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="56">
+      <c r="A82" s="6">
+        <v>46280</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="F82" s="8">
+        <v>47.236199999999997</v>
+      </c>
+      <c r="G82" s="8">
+        <v>38.896900000000002</v>
+      </c>
+      <c r="H82" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I82" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="J82" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="K82" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="L82" s="7" t="s">
+        <v>629</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -4901,7 +5945,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -7082,6 +8126,424 @@
         <v>563</v>
       </c>
     </row>
+    <row r="58" spans="1:12" ht="28">
+      <c r="A58" s="6">
+        <v>46268</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="F58" s="8">
+        <v>50.511400000000002</v>
+      </c>
+      <c r="G58" s="8">
+        <v>30.79</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>645</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="L58" s="7" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="56">
+      <c r="A59" s="6">
+        <v>46273</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="F59" s="8">
+        <v>50.450099999999999</v>
+      </c>
+      <c r="G59" s="8">
+        <v>30.523399999999999</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="L59" s="7" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="42">
+      <c r="A60" s="6">
+        <v>46273</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="F60" s="8">
+        <v>50.907699999999998</v>
+      </c>
+      <c r="G60" s="8">
+        <v>34.798099999999998</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="K60" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="L60" s="7" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="42">
+      <c r="A61" s="6">
+        <v>46273</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>658</v>
+      </c>
+      <c r="F61" s="8">
+        <v>47.838799999999999</v>
+      </c>
+      <c r="G61" s="8">
+        <v>35.139600000000002</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>660</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="L61" s="7" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="42">
+      <c r="A62" s="6">
+        <v>46274</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="F62" s="8">
+        <v>46.183999999999997</v>
+      </c>
+      <c r="G62" s="8">
+        <v>29.003</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="L62" s="7" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="28">
+      <c r="A63" s="6">
+        <v>46274</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="F63" s="8">
+        <v>50.907699999999998</v>
+      </c>
+      <c r="G63" s="8">
+        <v>34.798099999999998</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="L63" s="7" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="42">
+      <c r="A64" s="6">
+        <v>46276</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="F64" s="8">
+        <v>50.450099999999999</v>
+      </c>
+      <c r="G64" s="8">
+        <v>30.523399999999999</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="I64" s="7" t="s">
+        <v>672</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="K64" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="L64" s="7" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="42">
+      <c r="A65" s="6">
+        <v>46277</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="F65" s="8">
+        <v>46.482500000000002</v>
+      </c>
+      <c r="G65" s="8">
+        <v>30.723299999999998</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>676</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>677</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="L65" s="7" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="56">
+      <c r="A66" s="6">
+        <v>46278</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="F66" s="8">
+        <v>51.186</v>
+      </c>
+      <c r="G66" s="8">
+        <v>23.835000000000001</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="I66" s="7" t="s">
+        <v>680</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>681</v>
+      </c>
+      <c r="K66" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="L66" s="7" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="42">
+      <c r="A67" s="6">
+        <v>46280</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="F67" s="8">
+        <v>50.450099999999999</v>
+      </c>
+      <c r="G67" s="8">
+        <v>30.523399999999999</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>684</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>685</v>
+      </c>
+      <c r="K67" s="7" t="s">
+        <v>686</v>
+      </c>
+      <c r="L67" s="7" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="56">
+      <c r="A68" s="6">
+        <v>46280</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>687</v>
+      </c>
+      <c r="F68" s="8">
+        <v>46.482500000000002</v>
+      </c>
+      <c r="G68" s="8">
+        <v>30.723299999999998</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="I68" s="7" t="s">
+        <v>689</v>
+      </c>
+      <c r="J68" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="K68" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="L68" s="7" t="s">
+        <v>638</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/manual/ukrajna_oroszorszag_melysegi_csapasok.xlsx
+++ b/data/manual/ukrajna_oroszorszag_melysegi_csapasok.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orsolya\OneDrive - Budapesti Vasutas Sport Club - Zugló Közhasznú Egyesület\Asztal\Osint\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8735E32-7824-4BC7-97A8-5B60ED62CBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC3C408D-3622-45FE-A917-5E3582A820C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Összesítés" sheetId="1" r:id="rId1"/>
@@ -2692,7 +2692,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2733,6 +2733,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6932,10 +6935,10 @@
       <c r="E95" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="F95" s="9">
+      <c r="F95" s="15">
         <v>44.844999999999999</v>
       </c>
-      <c r="G95" s="9">
+      <c r="G95" s="15">
         <v>38.567</v>
       </c>
       <c r="H95" s="9" t="s">
@@ -6970,10 +6973,10 @@
       <c r="E96" s="9" t="s">
         <v>809</v>
       </c>
-      <c r="F96" s="9">
+      <c r="F96" s="15">
         <v>55.5</v>
       </c>
-      <c r="G96" s="9">
+      <c r="G96" s="15">
         <v>37.950000000000003</v>
       </c>
       <c r="H96" s="9" t="s">
@@ -7008,10 +7011,10 @@
       <c r="E97" s="9" t="s">
         <v>815</v>
       </c>
-      <c r="F97" s="9">
+      <c r="F97" s="15">
         <v>54.51</v>
       </c>
-      <c r="G97" s="9">
+      <c r="G97" s="15">
         <v>36.26</v>
       </c>
       <c r="H97" s="9" t="s">
@@ -7046,10 +7049,10 @@
       <c r="E98" s="9" t="s">
         <v>819</v>
       </c>
-      <c r="F98" s="9">
+      <c r="F98" s="15">
         <v>54.51</v>
       </c>
-      <c r="G98" s="9">
+      <c r="G98" s="15">
         <v>36.26</v>
       </c>
       <c r="H98" s="9" t="s">

--- a/data/manual/ukrajna_oroszorszag_melysegi_csapasok.xlsx
+++ b/data/manual/ukrajna_oroszorszag_melysegi_csapasok.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orsolya\OneDrive - Budapesti Vasutas Sport Club - Zugló Közhasznú Egyesület\Asztal\Osint\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC3C408D-3622-45FE-A917-5E3582A820C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B9B4FA-7ED5-44A2-85BC-202083C88C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Összesítés" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="862">
   <si>
     <t>MÉLYSÉGI CSAPÁSOK – 2026.07.13–07.27.</t>
   </si>
@@ -2587,15 +2587,6 @@
   </si>
   <si>
     <t>Orosz közlés két teherhajó elleni támadásról; független megerősítés nélkül, nem geolokált összesítő.</t>
-  </si>
-  <si>
-    <t>Priluki – lakóépület</t>
-  </si>
-  <si>
-    <t>Lakóépület / civil infrastruktúra</t>
-  </si>
-  <si>
-    <t>Orosz rakétatámadás rombolt le egy ötemeletes lakóépületet; Reuters későbbi jelentése szerint 22 halálos áldozat.</t>
   </si>
   <si>
     <t>Városi, ipari és energetikai infrastruktúra</t>
@@ -2724,6 +2715,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2733,9 +2727,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2979,7 +2970,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="RussiaUkraineTable" displayName="RussiaUkraineTable" ref="A1:L94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="RussiaUkraineTable" displayName="RussiaUkraineTable" ref="A1:L93">
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Dátum"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Támadó"/>
@@ -3156,16 +3147,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="32" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1"/>
@@ -3270,52 +3261,52 @@
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
     </row>
     <row r="10" spans="1:8" ht="34" customHeight="1">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
     </row>
     <row r="11" spans="1:8" ht="34" customHeight="1">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
     </row>
     <row r="12" spans="1:8" ht="34" customHeight="1">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6935,10 +6926,10 @@
       <c r="E95" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="F95" s="15">
+      <c r="F95" s="11">
         <v>44.844999999999999</v>
       </c>
-      <c r="G95" s="15">
+      <c r="G95" s="11">
         <v>38.567</v>
       </c>
       <c r="H95" s="9" t="s">
@@ -6973,10 +6964,10 @@
       <c r="E96" s="9" t="s">
         <v>809</v>
       </c>
-      <c r="F96" s="15">
+      <c r="F96" s="11">
         <v>55.5</v>
       </c>
-      <c r="G96" s="15">
+      <c r="G96" s="11">
         <v>37.950000000000003</v>
       </c>
       <c r="H96" s="9" t="s">
@@ -7011,10 +7002,10 @@
       <c r="E97" s="9" t="s">
         <v>815</v>
       </c>
-      <c r="F97" s="15">
+      <c r="F97" s="11">
         <v>54.51</v>
       </c>
-      <c r="G97" s="15">
+      <c r="G97" s="11">
         <v>36.26</v>
       </c>
       <c r="H97" s="9" t="s">
@@ -7049,10 +7040,10 @@
       <c r="E98" s="9" t="s">
         <v>819</v>
       </c>
-      <c r="F98" s="15">
+      <c r="F98" s="11">
         <v>54.51</v>
       </c>
-      <c r="G98" s="15">
+      <c r="G98" s="11">
         <v>36.26</v>
       </c>
       <c r="H98" s="9" t="s">
@@ -7081,7 +7072,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -10190,10 +10181,10 @@
       <c r="E82" s="9" t="s">
         <v>821</v>
       </c>
-      <c r="F82" s="9">
+      <c r="F82" s="11">
         <v>50.450099999999999</v>
       </c>
-      <c r="G82" s="9">
+      <c r="G82" s="11">
         <v>30.523399999999999</v>
       </c>
       <c r="H82" s="9" t="s">
@@ -10228,10 +10219,10 @@
       <c r="E83" s="9" t="s">
         <v>825</v>
       </c>
-      <c r="F83" s="9">
+      <c r="F83" s="11">
         <v>45.454999999999998</v>
       </c>
-      <c r="G83" s="9">
+      <c r="G83" s="11">
         <v>29.263000000000002</v>
       </c>
       <c r="H83" s="9" t="s">
@@ -10266,10 +10257,10 @@
       <c r="E84" s="9" t="s">
         <v>828</v>
       </c>
-      <c r="F84" s="9">
+      <c r="F84" s="11">
         <v>46.975000000000001</v>
       </c>
-      <c r="G84" s="9">
+      <c r="G84" s="11">
         <v>31.995000000000001</v>
       </c>
       <c r="H84" s="9" t="s">
@@ -10304,10 +10295,10 @@
       <c r="E85" s="9" t="s">
         <v>831</v>
       </c>
-      <c r="F85" s="9">
+      <c r="F85" s="11">
         <v>50.450099999999999</v>
       </c>
-      <c r="G85" s="9">
+      <c r="G85" s="11">
         <v>30.523399999999999</v>
       </c>
       <c r="H85" s="9" t="s">
@@ -10342,10 +10333,10 @@
       <c r="E86" s="9" t="s">
         <v>834</v>
       </c>
-      <c r="F86" s="9">
+      <c r="F86" s="11">
         <v>45.35</v>
       </c>
-      <c r="G86" s="9">
+      <c r="G86" s="11">
         <v>28.84</v>
       </c>
       <c r="H86" s="9" t="s">
@@ -10380,10 +10371,10 @@
       <c r="E87" s="9" t="s">
         <v>837</v>
       </c>
-      <c r="F87" s="9">
+      <c r="F87" s="11">
         <v>50.395000000000003</v>
       </c>
-      <c r="G87" s="9">
+      <c r="G87" s="11">
         <v>30.588999999999999</v>
       </c>
       <c r="H87" s="9" t="s">
@@ -10418,10 +10409,10 @@
       <c r="E88" s="9" t="s">
         <v>841</v>
       </c>
-      <c r="F88" s="9">
+      <c r="F88" s="11">
         <v>50.450099999999999</v>
       </c>
-      <c r="G88" s="9">
+      <c r="G88" s="11">
         <v>30.523399999999999</v>
       </c>
       <c r="H88" s="9" t="s">
@@ -10456,10 +10447,10 @@
       <c r="E89" s="9" t="s">
         <v>844</v>
       </c>
-      <c r="F89" s="9">
+      <c r="F89" s="11">
         <v>50.491</v>
       </c>
-      <c r="G89" s="9">
+      <c r="G89" s="11">
         <v>30.538</v>
       </c>
       <c r="H89" s="9" t="s">
@@ -10494,10 +10485,10 @@
       <c r="E90" s="9" t="s">
         <v>848</v>
       </c>
-      <c r="F90" s="9">
+      <c r="F90" s="11">
         <v>46.302999999999997</v>
       </c>
-      <c r="G90" s="9">
+      <c r="G90" s="11">
         <v>30.657</v>
       </c>
       <c r="H90" s="9" t="s">
@@ -10532,10 +10523,10 @@
       <c r="E91" s="9" t="s">
         <v>852</v>
       </c>
-      <c r="F91" s="9">
+      <c r="F91" s="11">
         <v>46.482500000000002</v>
       </c>
-      <c r="G91" s="9">
+      <c r="G91" s="11">
         <v>30.723299999999998</v>
       </c>
       <c r="H91" s="9" t="s">
@@ -10565,15 +10556,19 @@
         <v>29</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>249</v>
+        <v>178</v>
       </c>
       <c r="E92" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="F92" s="9"/>
-      <c r="G92" s="9"/>
+      <c r="F92" s="11">
+        <v>50.450099999999999</v>
+      </c>
+      <c r="G92" s="11">
+        <v>30.523399999999999</v>
+      </c>
       <c r="H92" s="9" t="s">
-        <v>188</v>
+        <v>342</v>
       </c>
       <c r="I92" s="9" t="s">
         <v>856</v>
@@ -10599,19 +10594,19 @@
         <v>29</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>858</v>
       </c>
-      <c r="F93" s="9">
-        <v>50.450099999999999</v>
-      </c>
-      <c r="G93" s="9">
-        <v>30.523399999999999</v>
+      <c r="F93" s="11">
+        <v>46.482500000000002</v>
+      </c>
+      <c r="G93" s="11">
+        <v>30.723299999999998</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>342</v>
+        <v>193</v>
       </c>
       <c r="I93" s="9" t="s">
         <v>859</v>
@@ -10623,45 +10618,7 @@
         <v>807</v>
       </c>
       <c r="L93" s="9" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="42">
-      <c r="A94" s="10">
-        <v>46302</v>
-      </c>
-      <c r="B94" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C94" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="E94" s="9" t="s">
         <v>861</v>
-      </c>
-      <c r="F94" s="9">
-        <v>46.482500000000002</v>
-      </c>
-      <c r="G94" s="9">
-        <v>30.723299999999998</v>
-      </c>
-      <c r="H94" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="I94" s="9" t="s">
-        <v>862</v>
-      </c>
-      <c r="J94" s="9" t="s">
-        <v>863</v>
-      </c>
-      <c r="K94" s="9" t="s">
-        <v>807</v>
-      </c>
-      <c r="L94" s="9" t="s">
-        <v>864</v>
       </c>
     </row>
   </sheetData>
